--- a/artfynd/A 36196-2023 artfynd.xlsx
+++ b/artfynd/A 36196-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36196-2023 artfynd.xlsx
+++ b/artfynd/A 36196-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112154536</v>
+        <v>112262801</v>
       </c>
       <c r="B2" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Totjärnen (Totjärnen), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574287</v>
+        <v>574174</v>
       </c>
       <c r="R2" t="n">
-        <v>6869379</v>
+        <v>6869344</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,58 +787,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112156020</v>
+        <v>112261646</v>
       </c>
       <c r="B3" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574216</v>
+        <v>574199</v>
       </c>
       <c r="R3" t="n">
-        <v>6869391</v>
+        <v>6869377</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +853,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,58 +895,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112155927</v>
+        <v>112260817</v>
       </c>
       <c r="B4" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Aven, Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574308</v>
+        <v>574117</v>
       </c>
       <c r="R4" t="n">
-        <v>6869358</v>
+        <v>6869478</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +961,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112155638</v>
+        <v>112154536</v>
       </c>
       <c r="B5" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,20 +1033,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Totjärnen (Totjärnen), Hls</t>
+          <t>Totjärnen, Totjärnen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574273</v>
+        <v>574288</v>
       </c>
       <c r="R5" t="n">
-        <v>6869391</v>
+        <v>6869378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112157446</v>
+        <v>112155588</v>
       </c>
       <c r="B6" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,23 +1145,23 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Totjärnen, Totjärnen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574261</v>
+        <v>574277</v>
       </c>
       <c r="R6" t="n">
-        <v>6869410</v>
+        <v>6869385</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,15 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112157358</v>
+        <v>112155638</v>
       </c>
       <c r="B7" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,23 +1257,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Totjärnen, Totjärnen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574224</v>
+        <v>574272</v>
       </c>
       <c r="R7" t="n">
-        <v>6869394</v>
+        <v>6869390</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,15 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112155588</v>
+        <v>112155792</v>
       </c>
       <c r="B8" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,20 +1369,20 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Totjärnen (Totjärnen), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574276</v>
+        <v>574308</v>
       </c>
       <c r="R8" t="n">
-        <v>6869385</v>
+        <v>6869365</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,15 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112155792</v>
+        <v>112155877</v>
       </c>
       <c r="B9" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,22 +1479,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>574308</v>
       </c>
       <c r="R9" t="n">
-        <v>6869366</v>
+        <v>6869358</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,15 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112157352</v>
+        <v>112156020</v>
       </c>
       <c r="B10" t="n">
-        <v>96775</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,23 +1589,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574227</v>
+        <v>574217</v>
       </c>
       <c r="R10" t="n">
-        <v>6869394</v>
+        <v>6869391</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1728,15 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112261791</v>
+        <v>112157352</v>
       </c>
       <c r="B11" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,23 +1701,23 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574278</v>
+        <v>574228</v>
       </c>
       <c r="R11" t="n">
-        <v>6869369</v>
+        <v>6869394</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,22 +1741,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,54 +1783,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112261646</v>
+        <v>112157358</v>
       </c>
       <c r="B12" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574199</v>
+        <v>574225</v>
       </c>
       <c r="R12" t="n">
-        <v>6869377</v>
+        <v>6869394</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1916,22 +1853,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,15 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112261698</v>
+        <v>112157446</v>
       </c>
       <c r="B13" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,23 +1925,23 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574220</v>
+        <v>574261</v>
       </c>
       <c r="R13" t="n">
-        <v>6869383</v>
+        <v>6869410</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,22 +1965,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,15 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112261976</v>
+        <v>112260996</v>
       </c>
       <c r="B14" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,23 +2037,23 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574259</v>
+        <v>574228</v>
       </c>
       <c r="R14" t="n">
-        <v>6869391</v>
+        <v>6869365</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2155,7 +2082,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,7 +2092,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,15 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112262069</v>
+        <v>112261698</v>
       </c>
       <c r="B15" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,20 +2149,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574245</v>
+        <v>574220</v>
       </c>
       <c r="R15" t="n">
-        <v>6869407</v>
+        <v>6869383</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
@@ -2272,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,55 +2231,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112262801</v>
+        <v>112261737</v>
       </c>
       <c r="B16" t="n">
-        <v>89875</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574174</v>
+        <v>574228</v>
       </c>
       <c r="R16" t="n">
-        <v>6869344</v>
+        <v>6869378</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2389,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2399,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,15 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112262458</v>
+        <v>112261791</v>
       </c>
       <c r="B17" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,23 +2373,23 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574228</v>
+        <v>574277</v>
       </c>
       <c r="R17" t="n">
-        <v>6869434</v>
+        <v>6869369</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2506,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,15 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112261737</v>
+        <v>112261976</v>
       </c>
       <c r="B18" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2584,14 +2491,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574228</v>
+        <v>574260</v>
       </c>
       <c r="R18" t="n">
-        <v>6869378</v>
+        <v>6869391</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2623,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2633,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,15 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112260996</v>
+        <v>112262069</v>
       </c>
       <c r="B19" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,23 +2597,23 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Aven (Aven), Hls</t>
+          <t>Aven, Aven, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574229</v>
+        <v>574245</v>
       </c>
       <c r="R19" t="n">
-        <v>6869365</v>
+        <v>6869407</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2740,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2750,7 +2652,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2774,6 +2676,118 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112262458</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Aven, Aven, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>574228</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6869434</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eleonor Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
